--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.57546063398295</v>
+        <v>1.88101235302223</v>
       </c>
       <c r="D2" t="n">
-        <v>37.16450579906162</v>
+        <v>6.039232192347512</v>
       </c>
       <c r="E2" t="n">
-        <v>17.42147056473721</v>
+        <v>2.830988966769796</v>
       </c>
       <c r="F2" t="n">
-        <v>10.21571534406007</v>
+        <v>1.660053743409761</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.702337847325362</v>
+        <v>0.6016299001903713</v>
       </c>
       <c r="D3" t="n">
-        <v>28.41656425466006</v>
+        <v>4.617691691382261</v>
       </c>
       <c r="E3" t="n">
-        <v>17.42147056473721</v>
+        <v>2.830988966769796</v>
       </c>
       <c r="F3" t="n">
-        <v>10.21571534406007</v>
+        <v>1.660053743409761</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.54821766188442</v>
+        <v>6.589085370056218</v>
       </c>
       <c r="D4" t="n">
-        <v>46.22096783500594</v>
+        <v>7.510907273188465</v>
       </c>
       <c r="E4" t="n">
-        <v>17.42147056473721</v>
+        <v>2.830988966769796</v>
       </c>
       <c r="F4" t="n">
-        <v>10.21571534406007</v>
+        <v>1.660053743409761</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.24137327505603</v>
+        <v>7.514223157196604</v>
       </c>
       <c r="D5" t="n">
-        <v>46.00236811221553</v>
+        <v>7.475384818235024</v>
       </c>
       <c r="E5" t="n">
-        <v>17.42147056473721</v>
+        <v>2.830988966769796</v>
       </c>
       <c r="F5" t="n">
-        <v>10.21571534406007</v>
+        <v>1.660053743409761</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.15993674674454</v>
+        <v>3.438489721345988</v>
       </c>
       <c r="D6" t="n">
-        <v>20.50490351694683</v>
+        <v>3.33204682150386</v>
       </c>
       <c r="E6" t="n">
-        <v>17.42147056473721</v>
+        <v>2.830988966769796</v>
       </c>
       <c r="F6" t="n">
-        <v>10.21571534406007</v>
+        <v>1.660053743409761</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.45239312313368</v>
+        <v>8.361013882509223</v>
       </c>
       <c r="D7" t="n">
-        <v>51.44362978279502</v>
+        <v>8.359589839704192</v>
       </c>
       <c r="E7" t="n">
-        <v>17.42147056473721</v>
+        <v>2.830988966769796</v>
       </c>
       <c r="F7" t="n">
-        <v>10.21571534406007</v>
+        <v>1.660053743409761</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.79825285507266</v>
+        <v>7.117216088949307</v>
       </c>
       <c r="D8" t="n">
-        <v>43.13057085782329</v>
+        <v>7.008717764396286</v>
       </c>
       <c r="E8" t="n">
-        <v>17.42147056473721</v>
+        <v>2.830988966769796</v>
       </c>
       <c r="F8" t="n">
-        <v>10.21571534406007</v>
+        <v>1.660053743409761</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
